--- a/etf_holdings/2026-10-08_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.39%753,000</t>
+          <t>9.52%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.39%</t>
+          <t>9.52%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.91%249,000</t>
+          <t>5.89%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.89%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11790</v>
+        <v>6000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.99%79,000</t>
+          <t>4.83%166,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>4.83%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>79000</v>
+        <v>166000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5950</v>
+        <v>10615</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.80%166,000</t>
+          <t>4.55%79,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>166000</v>
+        <v>79000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,25 +748,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1990</v>
+        <v>1270</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.99%404,000</t>
+          <t>3.99%625,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>404000</v>
+        <v>625000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1305</v>
+        <v>1965</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.95%625,000</t>
+          <t>3.93%404,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>625000</v>
+        <v>404000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6805</v>
+        <v>310</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.55%104,000</t>
+          <t>3.71%2,416,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>104000</v>
+        <v>2416000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>314</v>
+        <v>7165</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.41%2,416,000</t>
+          <t>3.46%104,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2416000</v>
+        <v>104000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.34%5885</t>
+          <t>+0.68%5925</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5885</v>
+        <v>5925</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.93%103,000</t>
+          <t>2.96%103,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.78%1,096,000</t>
+          <t>2.75%1,096,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8460</v>
+        <v>2960</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.38%59,000</t>
+          <t>2.48%161,600</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>59000</v>
+        <v>161600</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3545</v>
+        <v>8360</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.38%134,000</t>
+          <t>2.44%59,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>134000</v>
+        <v>59000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3140</v>
+        <v>3440</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.28%161,600</t>
+          <t>2.32%134,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>161600</v>
+        <v>134000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.23%621,000</t>
+          <t>2.22%621,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:12</t>
+          <t>2026-10-08 23:45:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1245</v>
+        <v>1285</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>-1.39%177</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5530</v>
+        <v>177</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.02%74,000</t>
+          <t>2.01%2,293,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>74000</v>
+        <v>2293000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,25 +1480,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.56%252</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>252</v>
+        <v>5575</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.00%1,616,000</t>
+          <t>2.00%74,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1507,11 +1507,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1616000</v>
+        <v>74000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.13%179.5</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>179.5</v>
+        <v>249</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.96%2,293,000</t>
+          <t>1.99%1,616,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2293000</v>
+        <v>1616000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17750</v>
+        <v>1475</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.86%20,300</t>
+          <t>1.82%251,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>20300</v>
+        <v>251000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,34 +1663,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1480</v>
+        <v>17485</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.82%251,000</t>
+          <t>1.76%20,300</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>251000</v>
+        <v>20300</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-9.95%5520</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.95%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5520</v>
+        <v>2330</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.80%61,000</t>
+          <t>1.74%148,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>61000</v>
+        <v>148000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.71%155,105</t>
+          <t>1.70%155,105</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.44%2060</t>
+          <t>0%2060</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,34 +1907,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>+1.72%5615</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2400</v>
+        <v>5615</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.68%148,000</t>
+          <t>1.65%61,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>148000</v>
+        <v>61000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>-1.85%635</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.46%485,000</t>
+          <t>1.53%485,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2015</v>
+        <v>1075</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.40%142,000</t>
+          <t>1.43%266,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>142000</v>
+        <v>266000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1100</v>
+        <v>2070</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.37%266,000</t>
+          <t>1.40%142,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>266000</v>
+        <v>142000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6845</v>
+        <v>6660</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.26%38,000</t>
+          <t>1.27%38,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.21%143,000</t>
+          <t>1.20%143,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:13</t>
+          <t>2026-10-08 23:45:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.45%335</t>
+          <t>-2.84%325.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.15%718,000</t>
+          <t>1.18%718,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+5.4%839</t>
+          <t>+4.53%877</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>839</v>
+        <v>877</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.10%286,000</t>
+          <t>1.17%286,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.05%1,474,000</t>
+          <t>1.07%1,474,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.14%796</t>
+          <t>+1.26%806</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.96%252,000</t>
+          <t>0.98%252,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.23%215.5</t>
+          <t>0%215.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.94%906,000</t>
+          <t>0.95%906,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.44%68.7</t>
+          <t>-2.04%67.3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>68.7</v>
+        <v>67.3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.92%2,781,000</t>
+          <t>0.93%2,781,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.82%365.5</t>
+          <t>-0.68%363</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>365.5</v>
+        <v>363</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.89%484,000</t>
+          <t>0.87%484,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.37%185</t>
+          <t>+1.89%188.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.87%948,000</t>
+          <t>0.86%948,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.63%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.77%650,000</t>
+          <t>0.79%650,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%780</t>
+          <t>+1.03%788</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.77%204,000</t>
+          <t>0.78%204,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.04%70.1</t>
+          <t>-0.86%69.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.04%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.75%2,255,500</t>
+          <t>0.77%2,255,500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.63%1600</t>
+          <t>+1.25%1620</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1600</v>
+        <v>1620</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.70%91,000</t>
+          <t>0.71%91,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2884玉山金</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.21%3015</t>
+          <t>-1.64%45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3015</v>
+        <v>45</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.66%44,000</t>
+          <t>0.66%2,962,622</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>44000</v>
+        <v>2962622</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2884玉山金</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.66%45.75</t>
+          <t>-3.32%2915</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>45.75</v>
+        <v>2915</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.65%2,962,622</t>
+          <t>0.65%44,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2962622</v>
+        <v>44000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.66%2455</t>
+          <t>-3.46%2370</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2455</v>
+        <v>2370</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.63%54,000</t>
+          <t>0.65%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:14</t>
+          <t>2026-10-08 23:45:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2315</v>
+        <v>2360</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.54%48,336</t>
+          <t>0.55%48,336</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:16</t>
+          <t>2026-10-08 23:45:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.52%582</t>
+          <t>0%582</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.54%195,000</t>
+          <t>0.55%195,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:16</t>
+          <t>2026-10-08 23:45:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.45%58,000</t>
+          <t>0.47%58,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:16</t>
+          <t>2026-10-08 23:45:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.91%488</t>
+          <t>-2.46%476</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>-2.46%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.44%182,000</t>
+          <t>0.43%182,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:16</t>
+          <t>2026-10-08 23:45:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.47%872</t>
+          <t>+0.23%874</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:16</t>
+          <t>2026-10-08 23:45:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+10%1815</t>
+          <t>-1.65%1785</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1815</v>
+        <v>1785</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.30%38,000</t>
+          <t>0.34%38,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
